--- a/outputs/step_disease_logistic/dm/dm_logistic_coefficients.xlsx
+++ b/outputs/step_disease_logistic/dm/dm_logistic_coefficients.xlsx
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6491</v>
+        <v>0.6411</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9138</v>
+        <v>1.8986</v>
       </c>
     </row>
     <row r="3">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6224</v>
+        <v>0.5461</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8633</v>
+        <v>1.7265</v>
       </c>
     </row>
     <row r="4">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.4462</v>
+        <v>-0.4095</v>
       </c>
       <c r="C4" t="n">
-        <v>0.64</v>
+        <v>0.664</v>
       </c>
     </row>
     <row r="5">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5855</v>
+        <v>0.6161</v>
       </c>
       <c r="C5" t="n">
-        <v>1.7959</v>
+        <v>1.8518</v>
       </c>
     </row>
     <row r="6">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.9486</v>
+        <v>-1.9664</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1425</v>
+        <v>0.14</v>
       </c>
     </row>
   </sheetData>
@@ -552,10 +552,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6868</v>
+        <v>0.6439</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9874</v>
+        <v>1.904</v>
       </c>
     </row>
     <row r="3">
@@ -565,10 +565,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.5441</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8299</v>
+        <v>1.7231</v>
       </c>
     </row>
     <row r="4">
@@ -578,10 +578,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.4323</v>
+        <v>-0.4109</v>
       </c>
       <c r="C4" t="n">
-        <v>0.649</v>
+        <v>0.663</v>
       </c>
     </row>
     <row r="5">
@@ -591,10 +591,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.503</v>
+        <v>0.6136</v>
       </c>
       <c r="C5" t="n">
-        <v>1.6537</v>
+        <v>1.8471</v>
       </c>
     </row>
     <row r="6">
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1196</v>
+        <v>0.0061</v>
       </c>
       <c r="C6" t="n">
-        <v>1.127</v>
+        <v>1.0061</v>
       </c>
     </row>
     <row r="7">
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.9639</v>
+        <v>-1.9677</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1403</v>
+        <v>0.1398</v>
       </c>
     </row>
   </sheetData>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3436</v>
+        <v>0.3237</v>
       </c>
       <c r="C2" t="n">
-        <v>1.41</v>
+        <v>1.3822</v>
       </c>
     </row>
     <row r="3">
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4441</v>
+        <v>0.3978</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5591</v>
+        <v>1.4886</v>
       </c>
     </row>
     <row r="4">
@@ -687,10 +687,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.2735</v>
+        <v>-0.2612</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7607</v>
+        <v>0.7701</v>
       </c>
     </row>
     <row r="5">
@@ -700,10 +700,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2815</v>
+        <v>0.3904</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3251</v>
+        <v>1.4776</v>
       </c>
     </row>
     <row r="6">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0917</v>
+        <v>0.0272</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0961</v>
+        <v>1.0276</v>
       </c>
     </row>
     <row r="7">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1303</v>
+        <v>0.0635</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1391</v>
+        <v>1.0655</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.5193</v>
+        <v>-0.4939</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5949</v>
+        <v>0.6102</v>
       </c>
     </row>
     <row r="9">
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.1237</v>
+        <v>0.1382</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8837</v>
+        <v>1.1482</v>
       </c>
     </row>
     <row r="10">
@@ -765,10 +765,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.8915</v>
+        <v>-1.8925</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1508</v>
+        <v>0.1507</v>
       </c>
     </row>
   </sheetData>
@@ -809,10 +809,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.519</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9246</v>
+        <v>1.6803</v>
       </c>
     </row>
     <row r="3">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5174</v>
+        <v>0.4239</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6776</v>
+        <v>1.5279</v>
       </c>
     </row>
     <row r="4">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.3886</v>
+        <v>-0.3821</v>
       </c>
       <c r="C4" t="n">
-        <v>0.678</v>
+        <v>0.6824</v>
       </c>
     </row>
     <row r="5">
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3177</v>
+        <v>0.393</v>
       </c>
       <c r="C5" t="n">
-        <v>1.374</v>
+        <v>1.4815</v>
       </c>
     </row>
     <row r="6">
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3258</v>
+        <v>0.3971</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3851</v>
+        <v>1.4875</v>
       </c>
     </row>
     <row r="7">
@@ -874,10 +874,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0504</v>
+        <v>-0.0445</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0517</v>
+        <v>0.9565</v>
       </c>
     </row>
     <row r="8">
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.961</v>
+        <v>-1.9337</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1407</v>
+        <v>0.1446</v>
       </c>
     </row>
   </sheetData>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.44</v>
+        <v>0.3489</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5527</v>
+        <v>1.4175</v>
       </c>
     </row>
     <row r="3">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4382</v>
+        <v>0.367</v>
       </c>
       <c r="C3" t="n">
-        <v>1.55</v>
+        <v>1.4434</v>
       </c>
     </row>
     <row r="4">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.2572</v>
+        <v>-0.2671</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7732</v>
+        <v>0.7655999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1888</v>
+        <v>0.2972</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2077</v>
+        <v>1.3461</v>
       </c>
     </row>
     <row r="6">
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.093</v>
+        <v>0.2067</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0974</v>
+        <v>1.2296</v>
       </c>
     </row>
     <row r="7">
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0939</v>
+        <v>0.0312</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0984</v>
+        <v>1.0317</v>
       </c>
     </row>
     <row r="8">
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1821</v>
+        <v>0.0403</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1998</v>
+        <v>1.0411</v>
       </c>
     </row>
     <row r="9">
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.483</v>
+        <v>-0.4239</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6169</v>
+        <v>0.6545</v>
       </c>
     </row>
     <row r="10">
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.0907</v>
+        <v>0.0927</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9133</v>
+        <v>1.0971</v>
       </c>
     </row>
     <row r="11">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1.9291</v>
+        <v>-1.9043</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1453</v>
+        <v>0.1489</v>
       </c>
     </row>
   </sheetData>
